--- a/data/trans_orig/P21D2_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P21D2_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitándolo, no pudo recibir atención dental en 2023</t>
+          <t>Población que, necesitándolo, no pudo recibir atención dental en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>68909</t>
+          <t>69918</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>99106</t>
+          <t>100459</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46007</t>
+          <t>45229</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>69871</t>
+          <t>69609</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>121481</t>
+          <t>119925</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>158608</t>
+          <t>158431</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,91%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>124889</t>
+          <t>123473</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>155676</t>
+          <t>154190</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>143601</t>
+          <t>143819</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>167140</t>
+          <t>168487</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>277247</t>
+          <t>279518</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>315978</t>
+          <t>316856</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>71,81%</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>4884</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>386</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5575</t>
+          <t>4809</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>749</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6555</t>
+          <t>7326</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -1069,82 +1069,82 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1145</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1776</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3764</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>1145</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3420</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1145</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45367</t>
+          <t>44870</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>70617</t>
+          <t>69125</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44605</t>
+          <t>44568</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>64954</t>
+          <t>65248</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>95205</t>
+          <t>96210</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>128637</t>
+          <t>128207</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,64%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>109547</t>
+          <t>111471</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>135420</t>
+          <t>135817</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>111190</t>
+          <t>110571</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>131935</t>
+          <t>131840</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>227841</t>
+          <t>228392</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>261889</t>
+          <t>260175</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,33%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>873</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3879</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4417</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>4091</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5497</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22649</t>
+          <t>20442</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>172265</t>
+          <t>177388</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20752</t>
+          <t>20983</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34295</t>
+          <t>34917</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32749</t>
+          <t>27654</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>196472</t>
+          <t>200578</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>40,59%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>344433</t>
+          <t>344432</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>235000</t>
+          <t>229887</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>392040</t>
+          <t>393231</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>42015</t>
+          <t>42466</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>56197</t>
+          <t>56406</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>288011</t>
+          <t>285840</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>459127</t>
+          <t>465320</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>94,17%</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8677</t>
+          <t>9637</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>1878</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9865</t>
+          <t>9482</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4453</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>164</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6864</t>
+          <t>6994</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>187100</t>
+          <t>190780</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>233356</t>
+          <t>235610</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>87252</t>
+          <t>87544</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>117257</t>
+          <t>115618</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>287857</t>
+          <t>285585</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>344479</t>
+          <t>339981</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>42,75%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>206304</t>
+          <t>203999</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>251789</t>
+          <t>248903</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>207049</t>
+          <t>209253</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>238160</t>
+          <t>238941</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>420732</t>
+          <t>422768</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>479754</t>
+          <t>476798</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>59,95%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14338</t>
+          <t>13091</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7056</t>
+          <t>7495</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17589</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>4846</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>17336</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>6154</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18501</t>
+          <t>17256</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13104</t>
+          <t>13990</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30008</t>
+          <t>29772</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>94078</t>
+          <t>93008</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>127265</t>
+          <t>126433</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>176607</t>
+          <t>177180</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>310347</t>
+          <t>301701</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>285900</t>
+          <t>283662</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>420952</t>
+          <t>426861</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>66,85%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>82064</t>
+          <t>82098</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>116245</t>
+          <t>117478</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>93878</t>
+          <t>99318</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>213928</t>
+          <t>212201</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>196948</t>
+          <t>183433</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>312511</t>
+          <t>313894</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>49,16%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1719</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1419</t>
+          <t>1469</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8670</t>
+          <t>9117</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8448</t>
+          <t>8482</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7582</t>
+          <t>7675</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>21954</t>
+          <t>20828</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>8398</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>35260</t>
+          <t>35767</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>19102</t>
+          <t>19292</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>48242</t>
+          <t>49616</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>27133</t>
+          <t>26337</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>59815</t>
+          <t>61152</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>152731</t>
+          <t>153685</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>187962</t>
+          <t>189127</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>186129</t>
+          <t>190523</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>240243</t>
+          <t>240916</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>54,5%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>56406</t>
+          <t>56426</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>91842</t>
+          <t>92341</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>118137</t>
+          <t>115966</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>150258</t>
+          <t>151510</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>182385</t>
+          <t>182954</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>236017</t>
+          <t>231991</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>52,48%</t>
         </is>
       </c>
     </row>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>21602</t>
+          <t>17276</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>27184</t>
+          <t>26794</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,47 +3851,47 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>8,41%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>13531</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>4445</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>35937</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>3,06%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
           <t>1,01%</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>8,53%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>13531</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>4489</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>37635</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9093</t>
+          <t>9318</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>2426</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10253</t>
+          <t>10388</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>350959</t>
+          <t>348318</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>688840</t>
+          <t>686974</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>580872</t>
+          <t>576722</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>787867</t>
+          <t>806537</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>920453</t>
+          <t>934318</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1346797</t>
+          <t>1356548</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,78%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>886335</t>
+          <t>888737</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1246953</t>
+          <t>1257059</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>712288</t>
+          <t>705574</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>908972</t>
+          <t>912597</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1724192</t>
+          <t>1718042</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2170471</t>
+          <t>2157024</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,02%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>29897</t>
+          <t>28942</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>12528</t>
+          <t>12395</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>38540</t>
+          <t>39888</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>21273</t>
+          <t>21863</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>54807</t>
+          <t>54429</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>15415</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>36798</t>
+          <t>38725</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>26156</t>
+          <t>26499</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>57597</t>
+          <t>55876</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>47199</t>
+          <t>44969</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>86369</t>
+          <t>85725</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D2_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P21D2_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>82622</t>
+          <t>90820</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>69918</t>
+          <t>74704</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>100459</t>
+          <t>108114</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>56287</t>
+          <t>60306</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45229</t>
+          <t>49003</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>69609</t>
+          <t>73627</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>138910</t>
+          <t>151126</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>119925</t>
+          <t>131327</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>158431</t>
+          <t>172413</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,1%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>141451</t>
+          <t>152664</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>123473</t>
+          <t>135625</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>154190</t>
+          <t>168140</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>157068</t>
+          <t>169888</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>143819</t>
+          <t>156594</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>168487</t>
+          <t>181296</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>298520</t>
+          <t>322552</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>279518</t>
+          <t>300948</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>316856</t>
+          <t>342627</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,75%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>926</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4884</t>
+          <t>4619</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1792</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>401</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4809</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2740</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>706</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7326</t>
+          <t>6934</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3764</t>
+          <t>3930</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t>4508</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>216293</t>
+          <t>233150</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>216293</t>
+          <t>233150</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>216293</t>
+          <t>233150</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>441232</t>
+          <t>477560</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>441232</t>
+          <t>477560</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>441232</t>
+          <t>477560</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>56586</t>
+          <t>66194</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44870</t>
+          <t>53267</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69125</t>
+          <t>80406</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>54334</t>
+          <t>59918</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44568</t>
+          <t>49388</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>65248</t>
+          <t>72024</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>110919</t>
+          <t>126112</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>96210</t>
+          <t>109156</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>128207</t>
+          <t>142601</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>36,23%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>124034</t>
+          <t>128941</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>111471</t>
+          <t>113618</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>135817</t>
+          <t>141637</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>122183</t>
+          <t>135121</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>110571</t>
+          <t>122890</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>131840</t>
+          <t>145960</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>246216</t>
+          <t>264062</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>228392</t>
+          <t>247405</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>260175</t>
+          <t>281142</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>71,44%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>866</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>4523</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>772</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4652</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>1639</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>5886</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>926</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>4571</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>810</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>67690</t>
+          <t>75048</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20442</t>
+          <t>62692</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>177388</t>
+          <t>91348</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>27676</t>
+          <t>29749</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20983</t>
+          <t>23182</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34917</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>95366</t>
+          <t>104797</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27654</t>
+          <t>90798</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>200578</t>
+          <t>121300</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>44,04%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>344432</t>
+          <t>110605</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>229887</t>
+          <t>94105</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>393231</t>
+          <t>122777</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>49594</t>
+          <t>54525</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>42466</t>
+          <t>46461</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>56406</t>
+          <t>61435</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>394026</t>
+          <t>165130</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>285840</t>
+          <t>149852</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>465320</t>
+          <t>180575</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>65,55%</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2258</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9637</t>
+          <t>8501</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>432</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>2288</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2613</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>437</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>8145</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>925</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4467</t>
+          <t>4509</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>474</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3899</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2840</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>838</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6994</t>
+          <t>7375</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>211865</t>
+          <t>239842</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>190780</t>
+          <t>215170</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>235610</t>
+          <t>263629</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>102092</t>
+          <t>118495</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>87544</t>
+          <t>103313</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>115618</t>
+          <t>135861</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>313956</t>
+          <t>358336</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>285585</t>
+          <t>328642</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>339981</t>
+          <t>387008</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>43,04%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>228236</t>
+          <t>253848</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>203999</t>
+          <t>230129</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>248903</t>
+          <t>277891</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>222628</t>
+          <t>250737</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>209253</t>
+          <t>234607</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>238941</t>
+          <t>266490</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>450864</t>
+          <t>504585</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>422768</t>
+          <t>475153</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>476798</t>
+          <t>533753</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>59,37%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>8542</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>3327</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13091</t>
+          <t>19954</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>8669</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>9723</t>
+          <t>12968</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>7419</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>24620</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>9905</t>
+          <t>9603</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4846</t>
+          <t>4503</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17336</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>10882</t>
+          <t>13604</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6154</t>
+          <t>7899</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17256</t>
+          <t>20546</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,22 +2841,22 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>20787</t>
+          <t>23208</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13990</t>
+          <t>15820</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29772</t>
+          <t>34063</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>456009</t>
+          <t>511835</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>456009</t>
+          <t>511835</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>456009</t>
+          <t>511835</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>339322</t>
+          <t>387262</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>339322</t>
+          <t>387262</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>339322</t>
+          <t>387262</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>795331</t>
+          <t>899097</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>795331</t>
+          <t>899097</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>795331</t>
+          <t>899097</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>110069</t>
+          <t>138332</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>93008</t>
+          <t>121966</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>126433</t>
+          <t>159562</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>221930</t>
+          <t>182918</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>177180</t>
+          <t>167300</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>301701</t>
+          <t>200171</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>331999</t>
+          <t>321250</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>283662</t>
+          <t>296396</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>426861</t>
+          <t>347061</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>53,03%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>98915</t>
+          <t>106308</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>82098</t>
+          <t>87070</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>117478</t>
+          <t>124769</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>172570</t>
+          <t>185873</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>99318</t>
+          <t>168353</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>212201</t>
+          <t>202774</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>271486</t>
+          <t>292181</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>183433</t>
+          <t>265625</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>313894</t>
+          <t>316448</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>48,35%</t>
         </is>
       </c>
     </row>
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>4188</t>
+          <t>4289</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1829</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>8876</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,17 +3297,17 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4188</t>
+          <t>4289</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8482</t>
+          <t>8679</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>13116</t>
+          <t>21367</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7675</t>
+          <t>13028</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>20828</t>
+          <t>31532</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>17750</t>
+          <t>15392</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>9700</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>35767</t>
+          <t>24159</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>30867</t>
+          <t>36759</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>19292</t>
+          <t>27499</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>49616</t>
+          <t>50044</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>222100</t>
+          <t>266007</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>222100</t>
+          <t>266007</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>222100</t>
+          <t>266007</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>416438</t>
+          <t>388472</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>416438</t>
+          <t>388472</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>416438</t>
+          <t>388472</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>638539</t>
+          <t>654479</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>638539</t>
+          <t>654479</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>638539</t>
+          <t>654479</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>42655</t>
+          <t>48104</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>26337</t>
+          <t>30866</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>61152</t>
+          <t>62934</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>171901</t>
+          <t>191067</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>153685</t>
+          <t>172727</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>189127</t>
+          <t>210235</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>214557</t>
+          <t>239171</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>190523</t>
+          <t>214907</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>240916</t>
+          <t>262470</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>55,53%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>75839</t>
+          <t>65078</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>56426</t>
+          <t>49915</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>92341</t>
+          <t>81746</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>132792</t>
+          <t>148623</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>115966</t>
+          <t>130107</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>151510</t>
+          <t>168229</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>208631</t>
+          <t>213701</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>182954</t>
+          <t>188802</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>231991</t>
+          <t>237449</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>50,24%</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>3536</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3806,12 +3806,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>17276</t>
+          <t>14579</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>7842</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3062</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>26794</t>
+          <t>18977</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>13531</t>
+          <t>11378</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>4749</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>35937</t>
+          <t>28297</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>720</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>4855</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>4648</t>
+          <t>7691</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9318</t>
+          <t>17200</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>5365</t>
+          <t>8410</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2426</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10388</t>
+          <t>17512</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>318756</t>
+          <t>355223</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>318756</t>
+          <t>355223</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>318756</t>
+          <t>355223</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>442084</t>
+          <t>472660</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>442084</t>
+          <t>472660</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>442084</t>
+          <t>472660</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>571487</t>
+          <t>658340</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>348318</t>
+          <t>611925</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>686974</t>
+          <t>703219</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>634219</t>
+          <t>642453</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>576722</t>
+          <t>607645</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>806537</t>
+          <t>675381</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1205707</t>
+          <t>1300793</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>934318</t>
+          <t>1249210</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1356548</t>
+          <t>1357572</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,79%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1012907</t>
+          <t>817444</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>888737</t>
+          <t>771419</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1257059</t>
+          <t>862446</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>856835</t>
+          <t>944768</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>705574</t>
+          <t>908247</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>912597</t>
+          <t>979349</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1869743</t>
+          <t>1762212</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1718042</t>
+          <t>1705848</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2157024</t>
+          <t>1813898</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>57,17%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>13353</t>
+          <t>16129</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>7773</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>28942</t>
+          <t>31383</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>20309</t>
+          <t>19575</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>12395</t>
+          <t>12702</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>39888</t>
+          <t>30691</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>33662</t>
+          <t>35704</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>21863</t>
+          <t>24090</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>54429</t>
+          <t>52562</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>25487</t>
+          <t>33541</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>15415</t>
+          <t>23542</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>38725</t>
+          <t>46253</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>36433</t>
+          <t>40555</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>26499</t>
+          <t>30729</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>55876</t>
+          <t>53503</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>74096</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>44969</t>
+          <t>58347</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>85725</t>
+          <t>91686</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1623234</t>
+          <t>1525454</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1623234</t>
+          <t>1525454</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1623234</t>
+          <t>1525454</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1547797</t>
+          <t>1647351</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1547797</t>
+          <t>1647351</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1547797</t>
+          <t>1647351</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>3171032</t>
+          <t>3172805</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3171032</t>
+          <t>3172805</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3171032</t>
+          <t>3172805</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
